--- a/HPB_Templates/TumorRegressionSystem_export.xlsx
+++ b/HPB_Templates/TumorRegressionSystem_export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roxana.martinez/OneDrive - Karolinska Institutet/Mac/Documents/deploy_HPB/HPB_Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/roxana.martinez/HPB-AI/deploy_HPB/HPB_Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BD2798-AEC7-934A-AEA7-499BB471CB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779AB744-797D-8640-AB0D-263C1E2DC5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="560" windowWidth="34560" windowHeight="22340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TumorRegressionSystems" sheetId="1" r:id="rId1"/>
@@ -34,37 +34,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>Complete Response</t>
-  </si>
-  <si>
     <t>No viable cancer cells are found in the specimen.</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Near Complete Response</t>
-  </si>
-  <si>
     <t>Single cancer cells or rare small groups of cells are present.</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>Partial Response</t>
-  </si>
-  <si>
     <t>Residual cancer is evident, but there is still more fibrosis than tumor.</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>Poor or No Response</t>
-  </si>
-  <si>
     <t>Extensive residual cancer with little to no evidence of tumor death.</t>
+  </si>
+  <si>
+    <t>Grade o - Complete Response</t>
+  </si>
+  <si>
+    <t>Grade 1 - Near Complete Response</t>
+  </si>
+  <si>
+    <t>Grade 2 - Partial Response</t>
+  </si>
+  <si>
+    <t>Grade 3 - oor or No Response</t>
   </si>
 </sst>
 </file>
@@ -458,43 +458,43 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
